--- a/output/exchange.xlsx
+++ b/output/exchange.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -494,6 +494,29 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>MYR</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>3.952</v>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-29 04:12:26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/exchange.xlsx
+++ b/output/exchange.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -517,6 +517,29 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>MYR</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>3.952</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-29 04:15:09</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/exchange.xlsx
+++ b/output/exchange.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -540,6 +540,52 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>MYR</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>3.952</v>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-29 05:43:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>MYR</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>3.952</v>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-29 05:43:50</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/exchange.xlsx
+++ b/output/exchange.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -586,6 +586,29 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>MYR</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>3.952</v>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-29 05:47:51</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/exchange.xlsx
+++ b/output/exchange.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -609,6 +609,98 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>MYR</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>3.952</v>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-29 05:49:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>MYR</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>3.952</v>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-29 05:51:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>MYR</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>3.952</v>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-29 06:10:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>MYR</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>3.952</v>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-29 06:11:07</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/exchange.xlsx
+++ b/output/exchange.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -701,6 +701,29 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>MYR</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>3.952</v>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-29 06:13:22</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/exchange.xlsx
+++ b/output/exchange.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -724,6 +724,29 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>MYR</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>3.952</v>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-29 06:31:10</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/exchange.xlsx
+++ b/output/exchange.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -747,6 +747,29 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>MYR</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>3.952</v>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-29 06:48:08</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/exchange.xlsx
+++ b/output/exchange.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -770,6 +770,75 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>MYR</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>3.952</v>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-29 07:03:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>MYR</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>3.952</v>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-29 07:04:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>MYR</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>3.952</v>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-29 07:04:56</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
